--- a/output/pdf_financials_xlsx/CASA.xlsx
+++ b/output/pdf_financials_xlsx/CASA.xlsx
@@ -1228,19 +1228,19 @@
         <v>-0.079073</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.079073</v>
+        <v>-0.079073</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.196092</v>
+        <v>-0.196092</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.024688</v>
+        <v>-0.024688</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.07335700000000001</v>
+        <v>-0.07335700000000001</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.048034</v>
+        <v>-0.048034</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-0.017598</v>
@@ -1252,7 +1252,7 @@
         <v>-0.661871</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.353383</v>
+        <v>-0.353383</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>0.0475</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.323742</v>
+        <v>-0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0</v>
@@ -1504,19 +1504,19 @@
         <v>-0.079073</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.079073</v>
+        <v>-0.079073</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.196092</v>
+        <v>-0.196092</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.024688</v>
+        <v>-0.024688</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.07335700000000001</v>
+        <v>-0.07335700000000001</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.048034</v>
+        <v>-0.048034</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-0.017598</v>
@@ -1525,10 +1525,10 @@
         <v>-0.581086</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.661871</v>
+        <v>-0.661871</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.353383</v>
+        <v>-0.353383</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
@@ -1672,19 +1672,19 @@
         <v>-0.079073</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.079073</v>
+        <v>-0.079073</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.196092</v>
+        <v>-0.196092</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.024688</v>
+        <v>-0.024688</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.07335700000000001</v>
+        <v>-0.07335700000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.048034</v>
+        <v>-0.048034</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-0.017598</v>
@@ -1693,10 +1693,10 @@
         <v>-0.581086</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.661871</v>
+        <v>-0.661871</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.353383</v>
+        <v>-0.353383</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.292863</v>
+        <v>-0.292863</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1.96092</v>
+        <v>-1.96092</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>2.445233</v>
+        <v>-2.445233</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2.4017</v>
+        <v>-2.4017</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>19.369533</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>33.09355</v>
+        <v>-33.09355</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -1910,19 +1910,19 @@
         <v>-0.079073</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.079073</v>
+        <v>-0.079073</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.196092</v>
+        <v>-0.196092</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.024688</v>
+        <v>-0.024688</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.07335700000000001</v>
+        <v>-0.07335700000000001</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.048034</v>
+        <v>-0.048034</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.017598</v>
@@ -1934,7 +1934,7 @@
         <v>-0.661871</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.353383</v>
+        <v>-0.353383</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         <v>-0.079073</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.079073</v>
+        <v>-0.079073</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.196092</v>
+        <v>-0.196092</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.024688</v>
+        <v>-0.024688</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.07335700000000001</v>
+        <v>-0.07335700000000001</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.048034</v>
+        <v>-0.048034</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.017598</v>
@@ -2046,7 +2046,7 @@
         <v>-0.661694</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.353383</v>
+        <v>-0.353383</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2160,19 +2160,19 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -2181,10 +2181,10 @@
         <v>-7.556643005093973</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-200</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="1" t="inlineStr">
         <is>
@@ -5478,31 +5478,31 @@
         <v>0.05748</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.05748</v>
+        <v>0.3064</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.465715</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.701247</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.7453689999999999</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.274519</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.267016</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.267016</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.267016</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.295962</v>
       </c>
     </row>
     <row r="93">
@@ -5784,10 +5784,10 @@
         <v>-0.079073</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.079073</v>
+        <v>-0.079073</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.196092</v>
+        <v>-0.196092</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-0.024688</v>
@@ -9058,7 +9058,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -9663,7 +9667,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -10650,7 +10658,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -11572,7 +11584,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -24880,10 +24896,10 @@
         </is>
       </c>
       <c r="M187" s="5" t="n">
-        <v>0.661871</v>
+        <v>-0.661871</v>
       </c>
       <c r="N187" s="5" t="n">
-        <v>0.353383</v>
+        <v>-0.353383</v>
       </c>
       <c r="O187" t="inlineStr">
         <is>
@@ -27569,16 +27585,16 @@
         </is>
       </c>
       <c r="H217" s="5" t="n">
-        <v>0.024688</v>
+        <v>-0.024688</v>
       </c>
       <c r="I217" s="5" t="n">
-        <v>0.07335700000000001</v>
+        <v>-0.07335700000000001</v>
       </c>
       <c r="J217" s="5" t="n">
-        <v>0.048034</v>
+        <v>-0.048034</v>
       </c>
       <c r="K217" s="5" t="n">
-        <v>0.023727</v>
+        <v>-0.023727</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -31367,10 +31383,10 @@
         </is>
       </c>
       <c r="F259" s="5" t="n">
-        <v>0.079073</v>
+        <v>-0.079073</v>
       </c>
       <c r="G259" s="5" t="n">
-        <v>0.196092</v>
+        <v>-0.196092</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CASA.xlsx
+++ b/output/pdf_financials_xlsx/CASA.xlsx
@@ -2302,19 +2302,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.215159</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.105653</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.045511</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.020356</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
@@ -2332,19 +2332,19 @@
         <v>0.306469</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.193752</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.523145</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.195335</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.036978</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.11433</v>
       </c>
     </row>
     <row r="35">
@@ -2406,19 +2406,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.215159</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.105653</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.045511</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.020356</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
@@ -2436,19 +2436,19 @@
         <v>0.306469</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.193752</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.523145</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.195335</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.036978</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.11433</v>
       </c>
     </row>
     <row r="37">
@@ -3042,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.020356</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.009903</v>
@@ -3060,19 +3060,19 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.208739</v>
+        <v>0.014987</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.561145</v>
+        <v>0.038</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.232477</v>
+        <v>0.037142</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.056067</v>
+        <v>0.019089</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.15562</v>
+        <v>0.04129</v>
       </c>
     </row>
     <row r="49">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
